--- a/data/Databaze_rustu_DD-test.xlsx
+++ b/data/Databaze_rustu_DD-test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-5460" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graf1" sheetId="1" state="visible" r:id="rId1"/>
@@ -39,12 +39,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -82,6 +88,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -567,6 +574,39 @@
                 <pt idx="120">
                   <v>34.58</v>
                 </pt>
+                <pt idx="121">
+                  <v>22.4</v>
+                </pt>
+                <pt idx="122">
+                  <v>22.4</v>
+                </pt>
+                <pt idx="123">
+                  <v>22.6</v>
+                </pt>
+                <pt idx="124">
+                  <v>22.6</v>
+                </pt>
+                <pt idx="125">
+                  <v>22.7</v>
+                </pt>
+                <pt idx="126">
+                  <v>22.7</v>
+                </pt>
+                <pt idx="127">
+                  <v>22.8</v>
+                </pt>
+                <pt idx="128">
+                  <v>22.8</v>
+                </pt>
+                <pt idx="129">
+                  <v>22.8</v>
+                </pt>
+                <pt idx="130">
+                  <v>23</v>
+                </pt>
+                <pt idx="131">
+                  <v>23</v>
+                </pt>
               </numCache>
             </numRef>
           </xVal>
@@ -939,6 +979,39 @@
                 <pt idx="120">
                   <v>13.9730769230788</v>
                 </pt>
+                <pt idx="121">
+                  <v>8.73076923076923</v>
+                </pt>
+                <pt idx="122">
+                  <v>9.153846153846153</v>
+                </pt>
+                <pt idx="123">
+                  <v>9.788461538461538</v>
+                </pt>
+                <pt idx="124">
+                  <v>10.42307692307692</v>
+                </pt>
+                <pt idx="125">
+                  <v>10.42307692307692</v>
+                </pt>
+                <pt idx="126">
+                  <v>8.51923076923077</v>
+                </pt>
+                <pt idx="127">
+                  <v>10.21153846153846</v>
+                </pt>
+                <pt idx="128">
+                  <v>8.51923076923077</v>
+                </pt>
+                <pt idx="129">
+                  <v>10.63461538461539</v>
+                </pt>
+                <pt idx="130">
+                  <v>9.365384615384615</v>
+                </pt>
+                <pt idx="131">
+                  <v>9.365384615384615</v>
+                </pt>
               </numCache>
             </numRef>
           </yVal>
@@ -1101,7 +1174,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="cs-CZ"/>
           </a:p>
@@ -1206,7 +1279,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="cs-CZ"/>
           </a:p>
@@ -1244,7 +1317,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="cs-CZ"/>
         </a:p>
@@ -4845,17 +4918,295 @@
         <v>34.58</v>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>8.73076923076923</v>
+      </c>
+      <c r="F123" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G123" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>9.153846153846153</v>
+      </c>
+      <c r="F124" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>9</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>9.788461538461538</v>
+      </c>
+      <c r="F125" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>10.42307692307692</v>
+      </c>
+      <c r="F126" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>7</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>10.42307692307692</v>
+      </c>
+      <c r="F127" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>6</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>8.51923076923077</v>
+      </c>
+      <c r="F128" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>10.21153846153846</v>
+      </c>
+      <c r="F129" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>8.51923076923077</v>
+      </c>
+      <c r="F130" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>10.63461538461539</v>
+      </c>
+      <c r="F131" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>9.365384615384615</v>
+      </c>
+      <c r="F132" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>UXCX2</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>XX01_naklon</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>9.365384615384615</v>
+      </c>
+      <c r="F133" t="n">
+        <v>23</v>
+      </c>
+    </row>
     <row r="134"/>
     <row r="135"/>
     <row r="136"/>
@@ -28810,7 +29161,7 @@
       <c r="K8635" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="G79:G89"/>
     <mergeCell ref="G57:G67"/>
     <mergeCell ref="G112:G122"/>
@@ -28822,6 +29173,7 @@
     <mergeCell ref="G90:G100"/>
     <mergeCell ref="G24:G34"/>
     <mergeCell ref="G101:G111"/>
+    <mergeCell ref="G123:G133"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
   <headerFooter>
